--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/24.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/24.xlsx
@@ -426,13 +426,13 @@
         <v>-14.93835988483382</v>
       </c>
       <c r="E2">
-        <v>-13.80313822143801</v>
+        <v>-13.40203353132004</v>
       </c>
       <c r="F2">
-        <v>4.576019842355562</v>
+        <v>2.292126419362239</v>
       </c>
       <c r="G2">
-        <v>-17.56095364540878</v>
+        <v>-15.64091939167109</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.78520551522818</v>
       </c>
       <c r="E3">
-        <v>-13.37393705670758</v>
+        <v>-13.72509522743315</v>
       </c>
       <c r="F3">
-        <v>4.841349234941855</v>
+        <v>2.287755952945069</v>
       </c>
       <c r="G3">
-        <v>-16.72974869860702</v>
+        <v>-14.85125922354771</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.5224539549284</v>
       </c>
       <c r="E4">
-        <v>-13.20515054846654</v>
+        <v>-14.08139092056754</v>
       </c>
       <c r="F4">
-        <v>5.068895133551656</v>
+        <v>2.415881195870874</v>
       </c>
       <c r="G4">
-        <v>-16.8750000846782</v>
+        <v>-14.32814824594323</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.16960940593834</v>
       </c>
       <c r="E5">
-        <v>-13.66016807479211</v>
+        <v>-14.80295739650928</v>
       </c>
       <c r="F5">
-        <v>5.311480870726686</v>
+        <v>2.647081851461827</v>
       </c>
       <c r="G5">
-        <v>-16.01567219714097</v>
+        <v>-14.05814765107488</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.75095059165264</v>
       </c>
       <c r="E6">
-        <v>-13.97398887570748</v>
+        <v>-13.9685398624493</v>
       </c>
       <c r="F6">
-        <v>5.170088495477644</v>
+        <v>2.591881104474074</v>
       </c>
       <c r="G6">
-        <v>-15.77469394451973</v>
+        <v>-13.3357076293112</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.30501763935024</v>
       </c>
       <c r="E7">
-        <v>-13.94325926511507</v>
+        <v>-15.95112928010343</v>
       </c>
       <c r="F7">
-        <v>4.760936297682496</v>
+        <v>2.579367786487385</v>
       </c>
       <c r="G7">
-        <v>-15.9541734975527</v>
+        <v>-13.49033028309218</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.85864455809034</v>
       </c>
       <c r="E8">
-        <v>-16.06863193490548</v>
+        <v>-15.84905995858444</v>
       </c>
       <c r="F8">
-        <v>5.283969132544908</v>
+        <v>2.699283908451446</v>
       </c>
       <c r="G8">
-        <v>-13.80027265945996</v>
+        <v>-12.92947838167856</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.44812681771604</v>
       </c>
       <c r="E9">
-        <v>-15.59991296441931</v>
+        <v>-17.40288429869725</v>
       </c>
       <c r="F9">
-        <v>5.183930514778424</v>
+        <v>3.068141002304816</v>
       </c>
       <c r="G9">
-        <v>-13.56583171129488</v>
+        <v>-12.56540352158633</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.0903609784975</v>
       </c>
       <c r="E10">
-        <v>-16.23182822070329</v>
+        <v>-17.47144551124752</v>
       </c>
       <c r="F10">
-        <v>5.771261227446135</v>
+        <v>3.515374906341463</v>
       </c>
       <c r="G10">
-        <v>-13.57892329004702</v>
+        <v>-11.86896390520555</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.80856744639134</v>
       </c>
       <c r="E11">
-        <v>-16.34955099570556</v>
+        <v>-18.10169117657892</v>
       </c>
       <c r="F11">
-        <v>5.019133446930685</v>
+        <v>3.942224345330021</v>
       </c>
       <c r="G11">
-        <v>-13.00522260912823</v>
+        <v>-12.03765847233263</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.61209684632159</v>
       </c>
       <c r="E12">
-        <v>-17.95496237368406</v>
+        <v>-18.36340994142432</v>
       </c>
       <c r="F12">
-        <v>5.825598815600171</v>
+        <v>3.680458589310571</v>
       </c>
       <c r="G12">
-        <v>-11.7387438811177</v>
+        <v>-10.99346245492637</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.50277230149235</v>
       </c>
       <c r="E13">
-        <v>-17.57982771398024</v>
+        <v>-19.26966972498118</v>
       </c>
       <c r="F13">
-        <v>5.646679740269506</v>
+        <v>4.098187703194306</v>
       </c>
       <c r="G13">
-        <v>-11.90017144067542</v>
+        <v>-10.57945318841221</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.48173213777119</v>
       </c>
       <c r="E14">
-        <v>-18.80156542977108</v>
+        <v>-19.51663628320079</v>
       </c>
       <c r="F14">
-        <v>6.406045795150618</v>
+        <v>4.396333698809904</v>
       </c>
       <c r="G14">
-        <v>-10.71618702025488</v>
+        <v>-11.01280546160192</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.52955618483328</v>
       </c>
       <c r="E15">
-        <v>-20.35980463352218</v>
+        <v>-20.25339105295742</v>
       </c>
       <c r="F15">
-        <v>6.727450690702021</v>
+        <v>4.354484577620473</v>
       </c>
       <c r="G15">
-        <v>-11.40250608522822</v>
+        <v>-10.18374001999258</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.62940366394346</v>
       </c>
       <c r="E16">
-        <v>-21.00645963679798</v>
+        <v>-20.92034279997766</v>
       </c>
       <c r="F16">
-        <v>6.849576896896752</v>
+        <v>4.562984652905109</v>
       </c>
       <c r="G16">
-        <v>-9.885957186557903</v>
+        <v>-9.839090405030532</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.74653034746221</v>
       </c>
       <c r="E17">
-        <v>-20.64987321887085</v>
+        <v>-21.56759171247291</v>
       </c>
       <c r="F17">
-        <v>6.60936360396334</v>
+        <v>4.654857224814796</v>
       </c>
       <c r="G17">
-        <v>-9.704864193367625</v>
+        <v>-9.684643976509454</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.85379567045166</v>
       </c>
       <c r="E18">
-        <v>-21.64600434228568</v>
+        <v>-22.74545490382826</v>
       </c>
       <c r="F18">
-        <v>7.46322981215582</v>
+        <v>4.922037190178943</v>
       </c>
       <c r="G18">
-        <v>-9.673673627737594</v>
+        <v>-9.58752688846463</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.92108112055771</v>
       </c>
       <c r="E19">
-        <v>-22.71419783539761</v>
+        <v>-23.38204667606401</v>
       </c>
       <c r="F19">
-        <v>7.280861414959897</v>
+        <v>5.203955468373699</v>
       </c>
       <c r="G19">
-        <v>-9.297161180413307</v>
+        <v>-9.050329638418797</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.92375391581218</v>
       </c>
       <c r="E20">
-        <v>-22.66639852626015</v>
+        <v>-24.04596657881713</v>
       </c>
       <c r="F20">
-        <v>7.734419075749517</v>
+        <v>5.057226750315823</v>
       </c>
       <c r="G20">
-        <v>-8.784752950260092</v>
+        <v>-8.631704575467554</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.85336573703695</v>
       </c>
       <c r="E21">
-        <v>-23.25322236719048</v>
+        <v>-25.02508614864545</v>
       </c>
       <c r="F21">
-        <v>7.982742085556335</v>
+        <v>5.497997731875828</v>
       </c>
       <c r="G21">
-        <v>-8.709288072481668</v>
+        <v>-8.70228344474371</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.70207663535063</v>
       </c>
       <c r="E22">
-        <v>-23.3676931777254</v>
+        <v>-24.48928450884065</v>
       </c>
       <c r="F22">
-        <v>7.737990995990388</v>
+        <v>5.306845326740619</v>
       </c>
       <c r="G22">
-        <v>-8.649941931808776</v>
+        <v>-7.768186442861584</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.48146277899193</v>
       </c>
       <c r="E23">
-        <v>-24.3359188742487</v>
+        <v>-25.71465628454071</v>
       </c>
       <c r="F23">
-        <v>7.631963281901663</v>
+        <v>5.340127472250298</v>
       </c>
       <c r="G23">
-        <v>-9.117856547267941</v>
+        <v>-7.551853619180459</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.20118967409148</v>
       </c>
       <c r="E24">
-        <v>-23.9163573130032</v>
+        <v>-25.3001616411115</v>
       </c>
       <c r="F24">
-        <v>8.124068191413153</v>
+        <v>5.415749132451865</v>
       </c>
       <c r="G24">
-        <v>-7.509246267453491</v>
+        <v>-7.535139632308152</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.88195676817775</v>
       </c>
       <c r="E25">
-        <v>-26.14922755151414</v>
+        <v>-27.10925480888224</v>
       </c>
       <c r="F25">
-        <v>7.71035168922858</v>
+        <v>5.623054701941664</v>
       </c>
       <c r="G25">
-        <v>-8.2780674722506</v>
+        <v>-7.665389679958794</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.54142003519061</v>
       </c>
       <c r="E26">
-        <v>-25.23082793125481</v>
+        <v>-26.23176016696114</v>
       </c>
       <c r="F26">
-        <v>8.481081288141295</v>
+        <v>5.634234348409846</v>
       </c>
       <c r="G26">
-        <v>-8.336613419706314</v>
+        <v>-7.321173448598871</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.19330234601635</v>
       </c>
       <c r="E27">
-        <v>-24.20779230487774</v>
+        <v>-26.83739390198161</v>
       </c>
       <c r="F27">
-        <v>7.393855698906167</v>
+        <v>5.239674670782414</v>
       </c>
       <c r="G27">
-        <v>-7.541951064946367</v>
+        <v>-7.198074230383289</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.85573489983242</v>
       </c>
       <c r="E28">
-        <v>-25.13880938114191</v>
+        <v>-28.23476677148812</v>
       </c>
       <c r="F28">
-        <v>7.447033572696284</v>
+        <v>5.255587608590192</v>
       </c>
       <c r="G28">
-        <v>-7.055222118591343</v>
+        <v>-6.499540796840427</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.534095469054565</v>
       </c>
       <c r="E29">
-        <v>-23.75804520372339</v>
+        <v>-27.62703151153729</v>
       </c>
       <c r="F29">
-        <v>7.462818941924032</v>
+        <v>5.456299373553707</v>
       </c>
       <c r="G29">
-        <v>-7.06475916858268</v>
+        <v>-6.172649466587132</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.241187465346151</v>
       </c>
       <c r="E30">
-        <v>-25.38941415248206</v>
+        <v>-27.70904912878</v>
       </c>
       <c r="F30">
-        <v>7.731163591856514</v>
+        <v>5.331089983885756</v>
       </c>
       <c r="G30">
-        <v>-6.803676877237578</v>
+        <v>-6.229015442309268</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.979241529696793</v>
       </c>
       <c r="E31">
-        <v>-25.17587263900468</v>
+        <v>-28.40985785452024</v>
       </c>
       <c r="F31">
-        <v>7.677467160072245</v>
+        <v>5.637476578424403</v>
       </c>
       <c r="G31">
-        <v>-6.62777796041132</v>
+        <v>-5.53447644799081</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.754947907783572</v>
       </c>
       <c r="E32">
-        <v>-24.9857676970333</v>
+        <v>-27.91507748297077</v>
       </c>
       <c r="F32">
-        <v>7.924837547365844</v>
+        <v>5.278284875426898</v>
       </c>
       <c r="G32">
-        <v>-7.397331479066237</v>
+        <v>-5.619607607617832</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.57138117916219</v>
       </c>
       <c r="E33">
-        <v>-26.12046656308971</v>
+        <v>-28.29686766382262</v>
       </c>
       <c r="F33">
-        <v>7.645712524053328</v>
+        <v>5.451266213214296</v>
       </c>
       <c r="G33">
-        <v>-6.297975649938935</v>
+        <v>-5.503667051071082</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.428770148868447</v>
       </c>
       <c r="E34">
-        <v>-24.32228803468062</v>
+        <v>-28.65369912121792</v>
       </c>
       <c r="F34">
-        <v>7.420126542718551</v>
+        <v>5.445545507930563</v>
       </c>
       <c r="G34">
-        <v>-6.623611212043904</v>
+        <v>-4.81055091255478</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.333068241126192</v>
       </c>
       <c r="E35">
-        <v>-24.34409654734729</v>
+        <v>-27.6734685673602</v>
       </c>
       <c r="F35">
-        <v>7.508321163359808</v>
+        <v>5.597673524719887</v>
       </c>
       <c r="G35">
-        <v>-6.735831457548317</v>
+        <v>-5.095779980623089</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.27985679919219</v>
       </c>
       <c r="E36">
-        <v>-27.31217240779071</v>
+        <v>-27.99161701447603</v>
       </c>
       <c r="F36">
-        <v>7.716798044357166</v>
+        <v>5.808380370765581</v>
       </c>
       <c r="G36">
-        <v>-6.482333379240399</v>
+        <v>-4.70567991307435</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.271846188766217</v>
       </c>
       <c r="E37">
-        <v>-24.00893239343363</v>
+        <v>-27.85955320076914</v>
       </c>
       <c r="F37">
-        <v>7.592556187815685</v>
+        <v>5.7830870004885</v>
       </c>
       <c r="G37">
-        <v>-6.564031409730108</v>
+        <v>-4.383694171907758</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.300975198180675</v>
       </c>
       <c r="E38">
-        <v>-24.25939180237742</v>
+        <v>-28.0772063934581</v>
       </c>
       <c r="F38">
-        <v>8.090153173207737</v>
+        <v>6.072460585308452</v>
       </c>
       <c r="G38">
-        <v>-7.445888717716353</v>
+        <v>-4.977445371286288</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.364116644190222</v>
       </c>
       <c r="E39">
-        <v>-23.22890116167228</v>
+        <v>-27.07556811182655</v>
       </c>
       <c r="F39">
-        <v>8.335548732613061</v>
+        <v>6.390631534519325</v>
       </c>
       <c r="G39">
-        <v>-6.704922852334127</v>
+        <v>-4.114996338590378</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.453176427141127</v>
       </c>
       <c r="E40">
-        <v>-24.64821129339654</v>
+        <v>-27.489132435919</v>
       </c>
       <c r="F40">
-        <v>8.324731911067305</v>
+        <v>6.527727996417449</v>
       </c>
       <c r="G40">
-        <v>-6.410947789885588</v>
+        <v>-4.719300167606188</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.562137811642405</v>
       </c>
       <c r="E41">
-        <v>-23.8183830578505</v>
+        <v>-25.75789952085482</v>
       </c>
       <c r="F41">
-        <v>8.0438640027393</v>
+        <v>6.217948408996935</v>
       </c>
       <c r="G41">
-        <v>-7.330585182849835</v>
+        <v>-4.616089601685707</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.687095682451455</v>
       </c>
       <c r="E42">
-        <v>-22.72958548335609</v>
+        <v>-26.60064009040976</v>
       </c>
       <c r="F42">
-        <v>7.820897319132174</v>
+        <v>6.442419407807544</v>
       </c>
       <c r="G42">
-        <v>-7.509053072353748</v>
+        <v>-5.294452422517628</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.818458759416943</v>
       </c>
       <c r="E43">
-        <v>-23.41117314708503</v>
+        <v>-26.04790996124495</v>
       </c>
       <c r="F43">
-        <v>7.668964797049911</v>
+        <v>6.550516383668463</v>
       </c>
       <c r="G43">
-        <v>-7.57823780401825</v>
+        <v>-5.440946523014176</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.955513859467505</v>
       </c>
       <c r="E44">
-        <v>-23.05429185115384</v>
+        <v>-26.24296968432685</v>
       </c>
       <c r="F44">
-        <v>8.137822403769237</v>
+        <v>6.908891316406808</v>
       </c>
       <c r="G44">
-        <v>-7.476081978912578</v>
+        <v>-5.545039520606454</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.089752890687066</v>
       </c>
       <c r="E45">
-        <v>-22.59006250210981</v>
+        <v>-25.18118459628914</v>
       </c>
       <c r="F45">
-        <v>8.385746140487907</v>
+        <v>6.718396634989422</v>
       </c>
       <c r="G45">
-        <v>-7.007790110859997</v>
+        <v>-5.278466833386241</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.219793884375742</v>
       </c>
       <c r="E46">
-        <v>-22.27453888455126</v>
+        <v>-24.55962329583794</v>
       </c>
       <c r="F46">
-        <v>7.816492061284086</v>
+        <v>6.976189540945045</v>
       </c>
       <c r="G46">
-        <v>-7.635380476256242</v>
+        <v>-6.282603585786459</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.33932486370338</v>
       </c>
       <c r="E47">
-        <v>-20.230805889773</v>
+        <v>-24.48835418950389</v>
       </c>
       <c r="F47">
-        <v>8.313187782941892</v>
+        <v>6.791831405247598</v>
       </c>
       <c r="G47">
-        <v>-6.848840147919247</v>
+        <v>-6.238769184101668</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.446244992305278</v>
       </c>
       <c r="E48">
-        <v>-21.31464037673423</v>
+        <v>-24.13320478269515</v>
       </c>
       <c r="F48">
-        <v>8.031236370051024</v>
+        <v>6.512217645167431</v>
       </c>
       <c r="G48">
-        <v>-8.006074879259234</v>
+        <v>-6.403319194190356</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.541217390180019</v>
       </c>
       <c r="E49">
-        <v>-20.70786450859943</v>
+        <v>-24.70383940588129</v>
       </c>
       <c r="F49">
-        <v>7.958104782262272</v>
+        <v>6.743978277122676</v>
       </c>
       <c r="G49">
-        <v>-8.003551594611924</v>
+        <v>-6.008188221814542</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.620367148106784</v>
       </c>
       <c r="E50">
-        <v>-20.10838583276236</v>
+        <v>-24.13832569225866</v>
       </c>
       <c r="F50">
-        <v>8.08341688948817</v>
+        <v>6.704587750384754</v>
       </c>
       <c r="G50">
-        <v>-7.34361279835949</v>
+        <v>-6.251752416953273</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.688256263454901</v>
       </c>
       <c r="E51">
-        <v>-19.92633812076115</v>
+        <v>-24.24041162662295</v>
       </c>
       <c r="F51">
-        <v>8.137549042526313</v>
+        <v>6.743620422404667</v>
       </c>
       <c r="G51">
-        <v>-8.203342740563755</v>
+        <v>-6.630955236578705</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.741203187668086</v>
       </c>
       <c r="E52">
-        <v>-18.62488366680155</v>
+        <v>-22.37659159322494</v>
       </c>
       <c r="F52">
-        <v>8.294377215959122</v>
+        <v>6.713298861992594</v>
       </c>
       <c r="G52">
-        <v>-8.809591574299944</v>
+        <v>-7.051530525739508</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.781525692835844</v>
       </c>
       <c r="E53">
-        <v>-21.28319226058263</v>
+        <v>-22.83339915363151</v>
       </c>
       <c r="F53">
-        <v>8.014657424851395</v>
+        <v>6.779439028901717</v>
       </c>
       <c r="G53">
-        <v>-8.382787048544744</v>
+        <v>-7.005040996805555</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.809114325959253</v>
       </c>
       <c r="E54">
-        <v>-18.72297421187135</v>
+        <v>-22.51383030824258</v>
       </c>
       <c r="F54">
-        <v>8.169560472440097</v>
+        <v>6.888795123214892</v>
       </c>
       <c r="G54">
-        <v>-8.437359442732786</v>
+        <v>-6.776733993057289</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.824674015040522</v>
       </c>
       <c r="E55">
-        <v>-18.08862932696234</v>
+        <v>-22.17796841482634</v>
       </c>
       <c r="F55">
-        <v>7.568618026609585</v>
+        <v>6.73058688968902</v>
       </c>
       <c r="G55">
-        <v>-8.769929142471751</v>
+        <v>-7.282463938546434</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.833139186769982</v>
       </c>
       <c r="E56">
-        <v>-18.47869478137891</v>
+        <v>-20.46320713587643</v>
       </c>
       <c r="F56">
-        <v>7.673944941875542</v>
+        <v>7.014059185131427</v>
       </c>
       <c r="G56">
-        <v>-9.223987231013583</v>
+        <v>-7.262669273056614</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.832789594325929</v>
       </c>
       <c r="E57">
-        <v>-19.73819764774641</v>
+        <v>-21.59690923121488</v>
       </c>
       <c r="F57">
-        <v>7.670540351850035</v>
+        <v>7.063067057415852</v>
       </c>
       <c r="G57">
-        <v>-9.39413076138873</v>
+        <v>-7.043651298563529</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.830842232637911</v>
       </c>
       <c r="E58">
-        <v>-17.44998586833213</v>
+        <v>-21.29866297276762</v>
       </c>
       <c r="F58">
-        <v>8.16258396217372</v>
+        <v>7.089210332648204</v>
       </c>
       <c r="G58">
-        <v>-9.736616069084745</v>
+        <v>-7.859112150108581</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.826998073271332</v>
       </c>
       <c r="E59">
-        <v>-18.13634972508462</v>
+        <v>-20.78651387145771</v>
       </c>
       <c r="F59">
-        <v>7.63375255549171</v>
+        <v>6.721135217623077</v>
       </c>
       <c r="G59">
-        <v>-9.433226661640653</v>
+        <v>-7.613326211322812</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.825158007520985</v>
       </c>
       <c r="E60">
-        <v>-17.29578959147522</v>
+        <v>-20.70705047917977</v>
       </c>
       <c r="F60">
-        <v>8.022417570680821</v>
+        <v>6.930486854597791</v>
       </c>
       <c r="G60">
-        <v>-9.937805268765118</v>
+        <v>-8.211064017691973</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.829128515394027</v>
       </c>
       <c r="E61">
-        <v>-18.03365742186691</v>
+        <v>-20.24123045019832</v>
       </c>
       <c r="F61">
-        <v>7.947342632965102</v>
+        <v>7.443054095693236</v>
       </c>
       <c r="G61">
-        <v>-9.21312131202537</v>
+        <v>-8.15754636431874</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.838966330474026</v>
       </c>
       <c r="E62">
-        <v>-16.68520107534423</v>
+        <v>-19.78711832394157</v>
       </c>
       <c r="F62">
-        <v>7.404687431065174</v>
+        <v>7.070129717892121</v>
       </c>
       <c r="G62">
-        <v>-9.529591855243234</v>
+        <v>-8.560856799498513</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.859246223992557</v>
       </c>
       <c r="E63">
-        <v>-16.93857603863804</v>
+        <v>-20.24640950472038</v>
       </c>
       <c r="F63">
-        <v>7.632226702735752</v>
+        <v>6.988199211550833</v>
       </c>
       <c r="G63">
-        <v>-9.946331960599693</v>
+        <v>-8.414816968560817</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.8851225337913</v>
       </c>
       <c r="E64">
-        <v>-16.57438509077515</v>
+        <v>-20.05820673353578</v>
       </c>
       <c r="F64">
-        <v>7.779768877583178</v>
+        <v>6.884172833107271</v>
       </c>
       <c r="G64">
-        <v>-10.870505522291</v>
+        <v>-8.76147163536884</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.919429945528558</v>
       </c>
       <c r="E65">
-        <v>-15.81426020089371</v>
+        <v>-19.78180636665711</v>
       </c>
       <c r="F65">
-        <v>7.82842386535401</v>
+        <v>6.893384278626401</v>
       </c>
       <c r="G65">
-        <v>-10.52729834371554</v>
+        <v>-8.549761134986282</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.956961104325952</v>
       </c>
       <c r="E66">
-        <v>-17.08198227247305</v>
+        <v>-19.95094589786076</v>
       </c>
       <c r="F66">
-        <v>7.56199771432641</v>
+        <v>7.375578600530798</v>
       </c>
       <c r="G66">
-        <v>-9.928482299830252</v>
+        <v>-9.53999045094964</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.995270154964276</v>
       </c>
       <c r="E67">
-        <v>-16.16578385421587</v>
+        <v>-20.62384919670948</v>
       </c>
       <c r="F67">
-        <v>7.838732069314447</v>
+        <v>6.889361726518406</v>
       </c>
       <c r="G67">
-        <v>-9.411937344872419</v>
+        <v>-8.723743765282661</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.03360448298212</v>
       </c>
       <c r="E68">
-        <v>-16.09921202989019</v>
+        <v>-19.37877873969575</v>
       </c>
       <c r="F68">
-        <v>7.143206633432287</v>
+        <v>7.093865757451938</v>
       </c>
       <c r="G68">
-        <v>-10.39317656183628</v>
+        <v>-9.13335653790538</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.06659935577704</v>
       </c>
       <c r="E69">
-        <v>-15.03601485000203</v>
+        <v>-19.45438795186426</v>
       </c>
       <c r="F69">
-        <v>7.663918382832057</v>
+        <v>7.320709200504165</v>
       </c>
       <c r="G69">
-        <v>-10.26921057641645</v>
+        <v>-9.277489219919268</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.09616948790477</v>
       </c>
       <c r="E70">
-        <v>-16.26546092601176</v>
+        <v>-18.59799992989593</v>
       </c>
       <c r="F70">
-        <v>7.825363876168069</v>
+        <v>7.16532901329145</v>
       </c>
       <c r="G70">
-        <v>-10.12987905370562</v>
+        <v>-9.328983546234387</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.1158678141601</v>
       </c>
       <c r="E71">
-        <v>-15.84111901853137</v>
+        <v>-18.62053110133313</v>
       </c>
       <c r="F71">
-        <v>7.561585187359817</v>
+        <v>7.238444033732146</v>
       </c>
       <c r="G71">
-        <v>-10.06576438803706</v>
+        <v>-9.589004569903199</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.12832354482913</v>
       </c>
       <c r="E72">
-        <v>-17.91075143913126</v>
+        <v>-19.25141636120856</v>
       </c>
       <c r="F72">
-        <v>7.898715809685965</v>
+        <v>7.023225898810806</v>
       </c>
       <c r="G72">
-        <v>-9.833378095865177</v>
+        <v>-10.10145848808676</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.13053050071015</v>
       </c>
       <c r="E73">
-        <v>-18.14304054852892</v>
+        <v>-19.63480760502613</v>
       </c>
       <c r="F73">
-        <v>7.191238688916213</v>
+        <v>7.314064037198907</v>
       </c>
       <c r="G73">
-        <v>-9.848851979056706</v>
+        <v>-9.861596328778225</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.12342369998551</v>
       </c>
       <c r="E74">
-        <v>-17.1206320570619</v>
+        <v>-17.7963595396115</v>
       </c>
       <c r="F74">
-        <v>7.582292715694998</v>
+        <v>7.325715853086685</v>
       </c>
       <c r="G74">
-        <v>-10.46692095892916</v>
+        <v>-10.00146044338564</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.11131023249714</v>
       </c>
       <c r="E75">
-        <v>-16.78894829423844</v>
+        <v>-18.44694348080059</v>
       </c>
       <c r="F75">
-        <v>7.406519779760166</v>
+        <v>7.17059577323845</v>
       </c>
       <c r="G75">
-        <v>-9.64662370302907</v>
+        <v>-10.29655943138065</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.09228332440683</v>
       </c>
       <c r="E76">
-        <v>-18.44689779547602</v>
+        <v>-19.17371393053234</v>
       </c>
       <c r="F76">
-        <v>7.337942555952006</v>
+        <v>7.518771846513527</v>
       </c>
       <c r="G76">
-        <v>-10.64961694929838</v>
+        <v>-10.40840764578083</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.07130169407719</v>
       </c>
       <c r="E77">
-        <v>-17.68544387797063</v>
+        <v>-20.1631085451783</v>
       </c>
       <c r="F77">
-        <v>7.407578433300944</v>
+        <v>7.569675023415557</v>
       </c>
       <c r="G77">
-        <v>-10.2090877392277</v>
+        <v>-9.935814576014394</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.04354240328219</v>
       </c>
       <c r="E78">
-        <v>-17.33053535741874</v>
+        <v>-19.78286543554495</v>
       </c>
       <c r="F78">
-        <v>6.93957073153689</v>
+        <v>7.280684144335699</v>
       </c>
       <c r="G78">
-        <v>-9.862809019640798</v>
+        <v>-9.549924334118826</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.01008283551067</v>
       </c>
       <c r="E79">
-        <v>-17.59284387827226</v>
+        <v>-19.97446553359326</v>
       </c>
       <c r="F79">
-        <v>7.005480612308036</v>
+        <v>7.509459340171255</v>
       </c>
       <c r="G79">
-        <v>-8.745538261129276</v>
+        <v>-9.845232181681126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.966788139597282</v>
       </c>
       <c r="E80">
-        <v>-19.27609889611201</v>
+        <v>-19.61199401521885</v>
       </c>
       <c r="F80">
-        <v>7.640024953465708</v>
+        <v>7.213415741023962</v>
       </c>
       <c r="G80">
-        <v>-9.206551373261833</v>
+        <v>-9.557727849701664</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.909122838450211</v>
       </c>
       <c r="E81">
-        <v>-19.54866169572654</v>
+        <v>-20.31485858056488</v>
       </c>
       <c r="F81">
-        <v>7.834151197576966</v>
+        <v>7.393100227834814</v>
       </c>
       <c r="G81">
-        <v>-9.199708611688525</v>
+        <v>-9.600993109065593</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.837069852053293</v>
       </c>
       <c r="E82">
-        <v>-20.31705147614439</v>
+        <v>-21.53376795944351</v>
       </c>
       <c r="F82">
-        <v>7.626865508904834</v>
+        <v>7.208967408070929</v>
       </c>
       <c r="G82">
-        <v>-9.248999469568744</v>
+        <v>-9.153452744395475</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.742424465130226</v>
       </c>
       <c r="E83">
-        <v>-20.62961800723966</v>
+        <v>-22.91045783655238</v>
       </c>
       <c r="F83">
-        <v>7.290612956025654</v>
+        <v>7.748537769762831</v>
       </c>
       <c r="G83">
-        <v>-8.812143577137757</v>
+        <v>-9.405584097909946</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.625514051672637</v>
       </c>
       <c r="E84">
-        <v>-21.62287095520638</v>
+        <v>-22.89571808956056</v>
       </c>
       <c r="F84">
-        <v>7.54754601661717</v>
+        <v>7.057772132977157</v>
       </c>
       <c r="G84">
-        <v>-8.835031974968048</v>
+        <v>-8.595382591343691</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.479620715067028</v>
       </c>
       <c r="E85">
-        <v>-20.8928485410073</v>
+        <v>-24.50522453390534</v>
       </c>
       <c r="F85">
-        <v>7.324634005258629</v>
+        <v>7.445734692608695</v>
       </c>
       <c r="G85">
-        <v>-9.068224987218581</v>
+        <v>-9.311009875096866</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.302487288888587</v>
       </c>
       <c r="E86">
-        <v>-24.90843490216499</v>
+        <v>-25.442346830817</v>
       </c>
       <c r="F86">
-        <v>7.268681100669133</v>
+        <v>7.856971062789286</v>
       </c>
       <c r="G86">
-        <v>-8.16453271684456</v>
+        <v>-8.444031200535376</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.092792254744896</v>
       </c>
       <c r="E87">
-        <v>-25.00251344509501</v>
+        <v>-26.56750161724895</v>
       </c>
       <c r="F87">
-        <v>7.656207939046799</v>
+        <v>7.332824902137511</v>
       </c>
       <c r="G87">
-        <v>-8.84771105607479</v>
+        <v>-8.522053302640796</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.847334623727827</v>
       </c>
       <c r="E88">
-        <v>-25.70549430035814</v>
+        <v>-27.04993864474104</v>
       </c>
       <c r="F88">
-        <v>8.190952232249991</v>
+        <v>8.148596150210047</v>
       </c>
       <c r="G88">
-        <v>-8.429281798967882</v>
+        <v>-8.2989260161613</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.572648404758519</v>
       </c>
       <c r="E89">
-        <v>-26.61976562856059</v>
+        <v>-28.64676325830545</v>
       </c>
       <c r="F89">
-        <v>7.407999243941566</v>
+        <v>7.793032696436804</v>
       </c>
       <c r="G89">
-        <v>-7.158941779707091</v>
+        <v>-8.211865516281444</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.268303291983505</v>
       </c>
       <c r="E90">
-        <v>-32.05761713130016</v>
+        <v>-29.47811779901337</v>
       </c>
       <c r="F90">
-        <v>7.563427476463643</v>
+        <v>7.971068732116085</v>
       </c>
       <c r="G90">
-        <v>-6.786991608555773</v>
+        <v>-7.526286597399687</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.944048693547915</v>
       </c>
       <c r="E91">
-        <v>-30.05116959119056</v>
+        <v>-31.27479286492287</v>
       </c>
       <c r="F91">
-        <v>7.508427194387367</v>
+        <v>7.763857596510205</v>
       </c>
       <c r="G91">
-        <v>-7.320541648407822</v>
+        <v>-6.936475011609146</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.605668455070832</v>
       </c>
       <c r="E92">
-        <v>-32.46061568578225</v>
+        <v>-33.08141902516666</v>
       </c>
       <c r="F92">
-        <v>7.397891504892606</v>
+        <v>7.715641643462857</v>
       </c>
       <c r="G92">
-        <v>-7.380599216981792</v>
+        <v>-7.539718878320964</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.261028058335203</v>
       </c>
       <c r="E93">
-        <v>-34.53404621813869</v>
+        <v>-34.98108127229793</v>
       </c>
       <c r="F93">
-        <v>7.522615471262516</v>
+        <v>7.921040311191412</v>
       </c>
       <c r="G93">
-        <v>-6.961814898610492</v>
+        <v>-7.366694391289522</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.921090319023341</v>
       </c>
       <c r="E94">
-        <v>-35.90078500091327</v>
+        <v>-36.31797092528097</v>
       </c>
       <c r="F94">
-        <v>7.085149675639681</v>
+        <v>7.755013946117918</v>
       </c>
       <c r="G94">
-        <v>-7.311263062131006</v>
+        <v>-7.101568056572786</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.59131178041729</v>
       </c>
       <c r="E95">
-        <v>-37.14934000222853</v>
+        <v>-39.1548385335504</v>
       </c>
       <c r="F95">
-        <v>7.641388446210716</v>
+        <v>7.755365173896705</v>
       </c>
       <c r="G95">
-        <v>-5.970222773970573</v>
+        <v>-6.855748178107333</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.286598306113039</v>
       </c>
       <c r="E96">
-        <v>-40.85274192773284</v>
+        <v>-40.71838554137463</v>
       </c>
       <c r="F96">
-        <v>6.750368303267872</v>
+        <v>8.006502976138236</v>
       </c>
       <c r="G96">
-        <v>-6.116325262778454</v>
+        <v>-6.214512756105634</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.009450221548224</v>
       </c>
       <c r="E97">
-        <v>-43.60804461879396</v>
+        <v>-43.80057088296771</v>
       </c>
       <c r="F97">
-        <v>6.461597769917159</v>
+        <v>7.465993245811559</v>
       </c>
       <c r="G97">
-        <v>-5.936348362900878</v>
+        <v>-6.685209119926631</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.774554390976021</v>
       </c>
       <c r="E98">
-        <v>-44.13722396314133</v>
+        <v>-45.55643234118813</v>
       </c>
       <c r="F98">
-        <v>6.477742650597721</v>
+        <v>7.592047570230365</v>
       </c>
       <c r="G98">
-        <v>-5.950712679641183</v>
+        <v>-6.412078242293541</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.582986497963101</v>
       </c>
       <c r="E99">
-        <v>-48.40357810918368</v>
+        <v>-47.52283461770374</v>
       </c>
       <c r="F99">
-        <v>6.661814171173799</v>
+        <v>7.429700813160108</v>
       </c>
       <c r="G99">
-        <v>-6.278400286994767</v>
+        <v>-6.425899524158894</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.449976767210645</v>
       </c>
       <c r="E100">
-        <v>-49.31536062549974</v>
+        <v>-50.19475951481326</v>
       </c>
       <c r="F100">
-        <v>6.557280831879724</v>
+        <v>7.048007338032956</v>
       </c>
       <c r="G100">
-        <v>-5.40748983107906</v>
+        <v>-5.630515298519503</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.371058818412702</v>
       </c>
       <c r="E101">
-        <v>-52.98243752645426</v>
+        <v>-51.56100198883453</v>
       </c>
       <c r="F101">
-        <v>5.439042823818587</v>
+        <v>7.214923369697057</v>
       </c>
       <c r="G101">
-        <v>-6.431152342276214</v>
+        <v>-5.734005214111233</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.373048163493011</v>
       </c>
       <c r="E102">
-        <v>-53.43050880683905</v>
+        <v>-53.95834770223133</v>
       </c>
       <c r="F102">
-        <v>5.353676249490487</v>
+        <v>7.113030865683107</v>
       </c>
       <c r="G102">
-        <v>-6.424421842720324</v>
+        <v>-5.592461085359436</v>
       </c>
     </row>
   </sheetData>
